--- a/downloads/korrigierte_referenz/FestivalCrew_3NF.xlsx
+++ b/downloads/korrigierte_referenz/FestivalCrew_3NF.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CREW" sheetId="1" r:id="Ra072e10632864cc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEAM" sheetId="2" r:id="R13b48907f3ff460f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WORKSHOP" sheetId="3" r:id="Rfd48b2fbb1914f67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAUM" sheetId="4" r:id="R4ac70806fbd64afd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CREW_WORKSHOP" sheetId="5" r:id="R6af5bd068ef04247"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CREW" sheetId="1" r:id="Rffd7e300ee6f4796"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEAM" sheetId="2" r:id="Rc401726562ed4da1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WORKSHOP" sheetId="3" r:id="R2cac4bed3ee44cc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAUM" sheetId="4" r:id="R47bc6315db6f4c7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CREW_WORKSHOP" sheetId="5" r:id="Rd18a9d4d5746493e"/>
   </x:sheets>
 </x:workbook>
 </file>
